--- a/artfynd/A 26072-2023 artfynd.xlsx
+++ b/artfynd/A 26072-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136186485</v>
       </c>
       <c r="B3" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136186486</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136186487</v>
       </c>
       <c r="B5" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136186489</v>
       </c>
       <c r="B6" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136186490</v>
       </c>
       <c r="B7" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136186491</v>
       </c>
       <c r="B8" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136186492</v>
       </c>
       <c r="B9" t="n">
-        <v>99259</v>
+        <v>99262</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26072-2023 artfynd.xlsx
+++ b/artfynd/A 26072-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136186485</v>
       </c>
       <c r="B3" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136186486</v>
       </c>
       <c r="B4" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136186487</v>
       </c>
       <c r="B5" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136186489</v>
       </c>
       <c r="B6" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136186490</v>
       </c>
       <c r="B7" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136186491</v>
       </c>
       <c r="B8" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136186492</v>
       </c>
       <c r="B9" t="n">
-        <v>99262</v>
+        <v>99263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26072-2023 artfynd.xlsx
+++ b/artfynd/A 26072-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136186499</v>
       </c>
       <c r="B2" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136186485</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136186486</v>
       </c>
       <c r="B4" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136186487</v>
       </c>
       <c r="B5" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136186489</v>
       </c>
       <c r="B6" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136186490</v>
       </c>
       <c r="B7" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136186491</v>
       </c>
       <c r="B8" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136186492</v>
       </c>
       <c r="B9" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26072-2023 artfynd.xlsx
+++ b/artfynd/A 26072-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136186485</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136186486</v>
       </c>
       <c r="B4" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136186487</v>
       </c>
       <c r="B5" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136186489</v>
       </c>
       <c r="B6" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136186490</v>
       </c>
       <c r="B7" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136186491</v>
       </c>
       <c r="B8" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136186492</v>
       </c>
       <c r="B9" t="n">
-        <v>99268</v>
+        <v>99270</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
